--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123302165</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56821</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Klubbenvägen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>649927</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6532780</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Thomas Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Thomas Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123302165</v>
       </c>
       <c r="B4" t="n">
-        <v>56821</v>
+        <v>56824</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123302165</v>
       </c>
       <c r="B4" t="n">
-        <v>56824</v>
+        <v>56830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123302165</v>
       </c>
       <c r="B4" t="n">
-        <v>56830</v>
+        <v>56833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123302165</v>
       </c>
       <c r="B4" t="n">
-        <v>56833</v>
+        <v>56834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128127176</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58210</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsväg 750m N Vretstugan, Stensund, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>650114</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6532725</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Trosa-Vagnhärad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128127176</v>
       </c>
       <c r="B5" t="n">
-        <v>58210</v>
+        <v>58211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128127176</v>
       </c>
       <c r="B5" t="n">
-        <v>58211</v>
+        <v>58223</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -1032,7 +1032,7 @@
         <v>128127176</v>
       </c>
       <c r="B5" t="n">
-        <v>58223</v>
+        <v>58227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115772564</v>
+        <v>123302165</v>
       </c>
       <c r="B2" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>sträckande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -748,17 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre gran intill  S sidan vägen</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,7 +776,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,55 +794,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118225174</v>
+        <v>128127176</v>
       </c>
       <c r="B3" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -872,12 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +895,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123302165</v>
+        <v>118225174</v>
       </c>
       <c r="B4" t="n">
-        <v>56834</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,49 +924,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100065</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>sträckande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klubbenvägen, Srm</t>
+          <t>Skogsväg 750m N Vretstugan, Stensund, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>649927</v>
+        <v>650114</v>
       </c>
       <c r="R4" t="n">
-        <v>6532780</v>
+        <v>6532725</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +994,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:37</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:37</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +1008,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,125 +1024,6 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>128127176</v>
-      </c>
-      <c r="B5" t="n">
-        <v>58227</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>102990</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Prunella modularis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Skogsväg 750m N Vretstugan, Stensund, Srm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>650114</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6532725</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Trosa</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Södermanland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Trosa-Vagnhärad</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Thomas Persson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Thomas Persson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2699-2023 artfynd.xlsx
+++ b/artfynd/A 2699-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302165</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128127176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,8 +1039,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118225174</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>